--- a/Design Files/BLDC-Board-v1.0/BOM/Client-BOM-BLDC-Board-v1.0.xlsx
+++ b/Design Files/BLDC-Board-v1.0/BOM/Client-BOM-BLDC-Board-v1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\muhunthancanagey-servocontrol\Design Files\BLDC-Board-v1.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="454">
   <si>
     <t>#</t>
   </si>
@@ -1351,6 +1351,36 @@
   </si>
   <si>
     <t>Custom</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>32V Blade fuse 15A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>0287015.PXCN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>P=2.54mm Shunts, Jumpers ROHS</t>
+  </si>
+  <si>
+    <t>X2541-A1NIB</t>
+  </si>
+  <si>
+    <t>Jumper</t>
+  </si>
+  <si>
+    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
+  </si>
+  <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGREEN </t>
   </si>
 </sst>
 </file>
@@ -1570,9 +1600,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1587,6 +1614,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1899,9 +1929,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1977,28 +2007,28 @@
       <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="14">
         <v>2</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>441</v>
       </c>
     </row>
@@ -3545,28 +3575,28 @@
       <c r="C53" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="F53" s="15" t="s">
+      <c r="F53" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="G53" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="H53" s="15" t="s">
+      <c r="H53" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I53" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="J53" s="15">
+      <c r="J53" s="14">
         <v>2</v>
       </c>
-      <c r="K53" s="18" t="s">
+      <c r="K53" s="17" t="s">
         <v>441</v>
       </c>
     </row>
@@ -4217,28 +4247,28 @@
       <c r="C74" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D74" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="E74" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="F74" s="15" t="s">
+      <c r="F74" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="G74" s="17" t="s">
+      <c r="G74" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="H74" s="15" t="s">
+      <c r="H74" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="I74" s="17" t="s">
+      <c r="I74" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="J74" s="15">
+      <c r="J74" s="14">
         <v>1</v>
       </c>
-      <c r="K74" s="18" t="s">
+      <c r="K74" s="17" t="s">
         <v>441</v>
       </c>
     </row>
@@ -4891,28 +4921,28 @@
       <c r="C95" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D95" s="15" t="s">
+      <c r="D95" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E95" s="16" t="s">
+      <c r="E95" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="F95" s="19" t="s">
+      <c r="F95" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="G95" s="17" t="s">
+      <c r="G95" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="H95" s="15" t="s">
+      <c r="H95" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="I95" s="17" t="s">
+      <c r="I95" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="J95" s="15">
+      <c r="J95" s="14">
         <v>1</v>
       </c>
-      <c r="K95" s="18" t="s">
+      <c r="K95" s="17" t="s">
         <v>441</v>
       </c>
     </row>
@@ -4979,6 +5009,99 @@
         <v>1</v>
       </c>
       <c r="K97" s="7"/>
+    </row>
+    <row r="98" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="11">
+        <f t="shared" ref="B98:B100" si="1">ROW(B98) - ROW($B$2)</f>
+        <v>96</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="J98" s="7">
+        <v>1</v>
+      </c>
+      <c r="K98" s="7"/>
+    </row>
+    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="11">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="J99" s="7">
+        <v>20</v>
+      </c>
+      <c r="K99" s="7"/>
+    </row>
+    <row r="100" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="11">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="G100" s="8">
+        <v>50173</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="J100" s="7">
+        <v>1</v>
+      </c>
+      <c r="K100" s="7"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C103"/>
